--- a/data/urban_canopy_financial.xlsx
+++ b/data/urban_canopy_financial.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +96,30 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A5C2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002D2D2D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -126,7 +150,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +172,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -201,6 +269,21 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,10 +650,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="21.42857142857143" customWidth="1" min="1" max="1"/>
+    <col width="107.1428571428571" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -581,99 +665,165 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  How to use this template</t>
         </is>
       </c>
+      <c r="B2" s="21" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="21" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
+      <c r="A4" s="22" t="inlineStr"/>
+      <c r="B4" s="21" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟦  BLUE cells</t>
         </is>
       </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Pre-filled input values — these are given to you. Do not change them.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟨  YELLOW cells</t>
         </is>
       </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Your task — write the correct Excel formula in each yellow cell. Each cell shows a hint describing what to calculate.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟩  GREEN cells</t>
         </is>
       </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Auto-calculated results — formulas are already written. They update automatically once you fill in the yellow cells.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="inlineStr"/>
+      <c r="A8" s="22" t="inlineStr"/>
+      <c r="B8" s="21" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Step 1</t>
         </is>
       </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Open the 'Financial Model' tab (second sheet at the bottom of the screen).</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Step 2</t>
         </is>
       </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Read row 3 — it explains the colour coding. Blue = given input, Yellow = write your formula, Green = auto-calculated result.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Step 3</t>
         </is>
       </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Start with the REVENUE section (rows 5–9). Each yellow cell in column D shows a hint (e.g. '= Qty × Price'). Write the formula using the values in columns B and C on the same row.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Step 4</t>
         </is>
       </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Repeat for COST OF GOODS SOLD (rows 12–15) and FIXED COSTS (rows 22–26). The hints in each yellow cell tell you exactly what to calculate.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Step 5</t>
         </is>
       </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Check your results: does the Operating Profit look reasonable for this company? Compare it to the financial snapshot on your company portfolio page.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="22" t="inlineStr"/>
+      <c r="B14" s="21" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tip</t>
         </is>
       </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A hint like '= Qty × Price' means: multiply the value in column B by column C on the same row. For row 5, that means typing =B5*C5 in cell D5.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tip</t>
         </is>
       </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL rows (e.g. TOTAL REVENUE, TOTAL COGS) already have SUM formulas written in green — do not click into or overwrite them.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tip</t>
         </is>
       </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>If a hint says '= C × 12', the rate in column C is a monthly figure. Multiply by 12 to get the annual amount — e.g. =C22*12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -737,6 +887,10 @@
           <t xml:space="preserve">  1.  REVENUE</t>
         </is>
       </c>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="19" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -851,6 +1005,10 @@
           <t xml:space="preserve">  2.  COST OF GOODS SOLD  (Variable Costs)</t>
         </is>
       </c>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="19" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -949,6 +1107,10 @@
           <t xml:space="preserve">  3.  GROSS PROFIT</t>
         </is>
       </c>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -993,6 +1155,10 @@
           <t xml:space="preserve">  4.  FIXED &amp; OPERATING COSTS</t>
         </is>
       </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -1115,6 +1281,10 @@
           <t xml:space="preserve">  5.  OPERATING PROFIT (EBIT)</t>
         </is>
       </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="19" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -1141,6 +1311,10 @@
           <t xml:space="preserve">  6.  BREAK-EVEN ANALYSIS</t>
         </is>
       </c>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="19" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
